--- a/Donnees/Statistiques Démographiques et sociales/Etat Civil/Theme_Etat_Civil.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Etat Civil/Theme_Etat_Civil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Etat Civil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639A31F0-D4DB-4F5D-9E66-DB936BB53ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C975E3-DC21-4D2B-88A5-ACBE945EBAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T7.1" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="52">
-  <si>
-    <t>Tableau 1.4.1: Nombre des actes de décès enregistrés par wilaya, 2020-2024</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="51">
   <si>
     <t>Année d'enrôlement~2024</t>
   </si>
@@ -52,15 +49,6 @@
     <t>Source : ANRPTS/2024</t>
   </si>
   <si>
-    <t>Tableau 1.4.2: Nombre des actes de mariage enregistrés par wilaya, 2020-2024</t>
-  </si>
-  <si>
-    <t>Tableau 1.4.3: Nombre des citoyens enrôlés par wilaya 2021-2024</t>
-  </si>
-  <si>
-    <t>Tableau 1.4.4: Nombre des citoyens mauritaniens enrôlés par âge 2020-2024</t>
-  </si>
-  <si>
     <t>Age</t>
   </si>
   <si>
@@ -73,12 +61,6 @@
     <t>5-11 ans</t>
   </si>
   <si>
-    <t>Total des enrôlés -Mauritanie</t>
-  </si>
-  <si>
-    <t>Tableau 1.4.5: Nombre des citoyens mauritaniens enrôlés par wilaya et par âge, 2024</t>
-  </si>
-  <si>
     <t>2024~1-5 ans</t>
   </si>
   <si>
@@ -133,9 +115,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Tableau 1.4.7: Le nombre de centres connectés par wilaya pour l'année 2024</t>
-  </si>
-  <si>
     <t>Nombre de centres</t>
   </si>
   <si>
@@ -182,6 +161,24 @@
   </si>
   <si>
     <t>Wilaya~Nouakchott-Sud</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.1: Nombre d'actes de décès enregistrés par wilaya, 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.2: Nombre d'actes de mariage enregistrés par wilaya, 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.3: Nombre de citoyens enrôlés par wilaya 2021-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.4: Nombre de citoyens mauritaniens enrôlés par âge 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.5: Nombre de citoyens mauritaniens enrôlés par wilaya et par âge, 2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.7: Nombre de centres connectés par wilaya 2024</t>
   </si>
 </sst>
 </file>
@@ -544,30 +541,30 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>5538</v>
@@ -587,7 +584,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -607,7 +604,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>191</v>
@@ -627,7 +624,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>276</v>
@@ -647,7 +644,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>284</v>
@@ -667,7 +664,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>219</v>
@@ -687,7 +684,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>480</v>
@@ -707,7 +704,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>341</v>
@@ -727,7 +724,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>90</v>
@@ -747,7 +744,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>343</v>
@@ -767,7 +764,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>77</v>
@@ -787,7 +784,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B14">
         <v>107</v>
@@ -807,7 +804,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B15">
         <v>194</v>
@@ -827,7 +824,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>36</v>
@@ -847,7 +844,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>641</v>
@@ -867,7 +864,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>1404</v>
@@ -887,7 +884,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>852</v>
@@ -907,7 +904,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -922,30 +919,30 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>47763</v>
@@ -965,7 +962,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>135</v>
@@ -985,7 +982,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>2730</v>
@@ -1005,7 +1002,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>2821</v>
@@ -1025,7 +1022,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>4326</v>
@@ -1045,7 +1042,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>2876</v>
@@ -1065,7 +1062,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>5594</v>
@@ -1085,7 +1082,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>3457</v>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>895</v>
@@ -1125,7 +1122,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>2168</v>
@@ -1145,7 +1142,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>801</v>
@@ -1165,7 +1162,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B14">
         <v>2360</v>
@@ -1185,7 +1182,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B15">
         <v>986</v>
@@ -1205,7 +1202,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>221</v>
@@ -1225,7 +1222,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>2914</v>
@@ -1245,7 +1242,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>12482</v>
@@ -1265,7 +1262,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>3132</v>
@@ -1285,7 +1282,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1299,31 +1296,32 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>244059</v>
@@ -1340,7 +1338,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>3553</v>
@@ -1357,7 +1355,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>37936</v>
@@ -1374,7 +1372,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>23999</v>
@@ -1391,7 +1389,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>24856</v>
@@ -1408,7 +1406,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>28094</v>
@@ -1425,7 +1423,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>18533</v>
@@ -1442,7 +1440,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>15099</v>
@@ -1459,7 +1457,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>2858</v>
@@ -1476,7 +1474,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>5330</v>
@@ -1493,7 +1491,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>5822</v>
@@ -1510,7 +1508,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B14">
         <v>19696</v>
@@ -1527,7 +1525,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B15">
         <v>3278</v>
@@ -1544,7 +1542,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>629</v>
@@ -1561,7 +1559,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>13668</v>
@@ -1578,7 +1576,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>24942</v>
@@ -1595,7 +1593,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>15766</v>
@@ -1612,7 +1610,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1624,35 +1622,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="80.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>514502</v>
@@ -1672,7 +1674,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>68813</v>
@@ -1692,7 +1694,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>186737</v>
@@ -1712,7 +1714,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>113606</v>
@@ -1732,7 +1734,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1747,39 +1749,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>59614</v>
@@ -1808,7 +1810,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>981</v>
@@ -1837,7 +1839,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>7531</v>
@@ -1866,7 +1868,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>6462</v>
@@ -1895,7 +1897,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>5976</v>
@@ -1924,7 +1926,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>6727</v>
@@ -1953,7 +1955,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>3794</v>
@@ -1982,7 +1984,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>4394</v>
@@ -2011,7 +2013,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>705</v>
@@ -2040,7 +2042,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>1092</v>
@@ -2069,7 +2071,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>1865</v>
@@ -2098,7 +2100,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B14">
         <v>4147</v>
@@ -2127,7 +2129,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B15">
         <v>421</v>
@@ -2156,7 +2158,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>173</v>
@@ -2185,7 +2187,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>8750</v>
@@ -2214,7 +2216,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>3142</v>
@@ -2243,7 +2245,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>3454</v>
@@ -2272,7 +2274,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2287,32 +2289,32 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>5914</v>
@@ -2332,7 +2334,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -2352,7 +2354,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -2372,7 +2374,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2390,18 +2392,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>117</v>
@@ -2409,7 +2411,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -2417,7 +2419,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>14</v>
@@ -2425,7 +2427,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>9</v>
@@ -2433,7 +2435,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>11</v>
@@ -2441,7 +2443,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -2449,7 +2451,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>16</v>
@@ -2457,7 +2459,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>15</v>
@@ -2465,7 +2467,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -2473,7 +2475,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -2481,7 +2483,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -2489,7 +2491,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -2497,7 +2499,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -2505,7 +2507,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -2513,7 +2515,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -2521,7 +2523,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -2529,7 +2531,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2537,7 +2539,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
